--- a/sheets/대금율보/검수/대금산조 중모리.xlsx
+++ b/sheets/대금율보/검수/대금산조 중모리.xlsx
@@ -13895,7 +13895,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?
+          <t xml:space="preserve">汰
 淋</t>
         </is>
       </c>
@@ -14533,7 +14533,7 @@
       <c r="K17" s="22"/>
       <c r="L17" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?
+          <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
@@ -14720,13 +14720,13 @@
       <c r="H20" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潕潢
-潕?</t>
+潕</t>
         </is>
       </c>
       <c r="I20" s="26"/>
       <c r="J20" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">林?
+          <t xml:space="preserve">林
 太</t>
         </is>
       </c>
@@ -14898,7 +14898,7 @@
       <c r="B23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">林太
-林?</t>
+林</t>
         </is>
       </c>
       <c r="C23" s="26"/>
@@ -14961,7 +14961,7 @@
       <c r="T23" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㳞
-淋?</t>
+淋</t>
         </is>
       </c>
       <c r="U23" s="26"/>
@@ -15030,8 +15030,8 @@
       <c r="S24" s="22"/>
       <c r="T24" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
-淋?</t>
+          <t xml:space="preserve">淋
+淋</t>
         </is>
       </c>
       <c r="U24" s="26"/>
@@ -15153,7 +15153,7 @@
       <c r="R26" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">淋㳞
-淋?</t>
+淋</t>
         </is>
       </c>
       <c r="S26" s="26"/>
@@ -15338,7 +15338,7 @@
       <c r="B31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋∧
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="C31" s="26"/>
@@ -15378,7 +15378,7 @@
       <c r="N31" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋∧
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="O31" s="26"/>
@@ -15391,7 +15391,7 @@
       <c r="Q31" s="22"/>
       <c r="R31" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰?</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="S31" s="26"/>
@@ -15494,8 +15494,8 @@
       </c>
       <c r="J33" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">無?
-仲?</t>
+          <t xml:space="preserve">無
+仲</t>
         </is>
       </c>
       <c r="K33" s="26" t="inlineStr">
@@ -15538,7 +15538,7 @@
       <c r="B34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋∧
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="C34" s="26"/>
@@ -15578,7 +15578,7 @@
       <c r="N34" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋∧
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="O34" s="26"/>
@@ -15678,7 +15678,7 @@
       <c r="C36" s="22"/>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="E36" s="26" t="inlineStr">
@@ -15739,7 +15739,7 @@
       <c r="B37" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋∧
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="C37" s="26"/>
@@ -15779,7 +15779,7 @@
       <c r="N37" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋∧
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="O37" s="26"/>
@@ -15821,7 +15821,7 @@
       <c r="F38" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞ㄷ
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="G38" s="26" t="inlineStr">
@@ -15938,7 +15938,7 @@
       <c r="B40" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋∧
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="C40" s="26"/>
@@ -15962,7 +15962,7 @@
       <c r="I40" s="22"/>
       <c r="J40" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K40" s="26" t="inlineStr">
@@ -15979,7 +15979,7 @@
       <c r="N40" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞淋∧
-㳞?</t>
+㳞</t>
         </is>
       </c>
       <c r="O40" s="26"/>
@@ -16034,7 +16034,7 @@
       <c r="I41" s="22"/>
       <c r="J41" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K41" s="26" t="inlineStr">
@@ -16050,7 +16050,7 @@
       <c r="M41" s="22"/>
       <c r="N41" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋?
+          <t xml:space="preserve">淋
 汰</t>
         </is>
       </c>
@@ -16593,7 +16593,7 @@
       <c r="M55" s="22"/>
       <c r="N55" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="O55" s="26" t="inlineStr">

--- a/sheets/대금율보/검수/대금산조 중모리.xlsx
+++ b/sheets/대금율보/검수/대금산조 중모리.xlsx
@@ -13650,32 +13650,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="15.29" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="152.99" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="152.99" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="152.99" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="22"/>
@@ -13877,7 +13877,7 @@
       </c>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="152.99" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="152.99" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -14016,7 +14016,7 @@
       </c>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="152.99" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="152.99" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="152.99" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="U10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="152.99" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="152.99" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="152.99" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="152.99" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -14467,10 +14467,10 @@
       </c>
       <c r="U14" s="22"/>
     </row>
-    <row r="15">
+    <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60" customHeight="1">
+    <row r="16" ht="102.56" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
       <c r="T16" s="20"/>
       <c r="U16" s="20"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="152.99" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
       </c>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="152.99" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="152.99" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="152.99" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
       </c>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="152.99" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
       </c>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="152.99" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
       </c>
       <c r="U22" s="22"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="152.99" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="25" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="U23" s="26"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="152.99" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="U24" s="26"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="152.99" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
       </c>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="152.99" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
       </c>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="152.99" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
       </c>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="152.99" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -15303,10 +15303,10 @@
       </c>
       <c r="U28" s="22"/>
     </row>
-    <row r="29">
+    <row r="29" ht="6.0" customHeight="true">
       <c r="A29" s="0"/>
     </row>
-    <row r="30" ht="60" customHeight="1">
+    <row r="30" ht="102.56" customHeight="true">
       <c r="A30" s="0"/>
       <c r="B30" s="20" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
       <c r="T30" s="20"/>
       <c r="U30" s="20"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="152.99" customHeight="true">
       <c r="A31" s="0"/>
       <c r="B31" s="25" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="152.99" customHeight="true">
       <c r="A32" s="0"/>
       <c r="B32" s="21" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="U32" s="22"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="152.99" customHeight="true">
       <c r="A33" s="0"/>
       <c r="B33" s="21" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="152.99" customHeight="true">
       <c r="A34" s="0"/>
       <c r="B34" s="25" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" ht="56" customHeight="1">
+    <row r="35" ht="152.99" customHeight="true">
       <c r="A35" s="0"/>
       <c r="B35" s="21" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="U35" s="22"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="152.99" customHeight="true">
       <c r="A36" s="0"/>
       <c r="B36" s="21" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="U36" s="22"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="152.99" customHeight="true">
       <c r="A37" s="0"/>
       <c r="B37" s="25" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="U37" s="22"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="152.99" customHeight="true">
       <c r="A38" s="0"/>
       <c r="B38" s="21" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
       </c>
       <c r="U38" s="22"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="152.99" customHeight="true">
       <c r="A39" s="0"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
       </c>
       <c r="U39" s="22"/>
     </row>
-    <row r="40" ht="56" customHeight="1">
+    <row r="40" ht="152.99" customHeight="true">
       <c r="A40" s="0"/>
       <c r="B40" s="25" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="U40" s="22"/>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="152.99" customHeight="true">
       <c r="A41" s="0"/>
       <c r="B41" s="21" t="inlineStr">
         <is>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="U41" s="22"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="152.99" customHeight="true">
       <c r="A42" s="0"/>
       <c r="B42" s="21" t="inlineStr">
         <is>
@@ -16145,10 +16145,10 @@
       </c>
       <c r="U42" s="22"/>
     </row>
-    <row r="43">
+    <row r="43" ht="6.0" customHeight="true">
       <c r="A43" s="0"/>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="102.56" customHeight="true">
       <c r="A44" s="0"/>
       <c r="B44" s="20" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
       <c r="T44" s="20"/>
       <c r="U44" s="20"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="152.99" customHeight="true">
       <c r="A45" s="0"/>
       <c r="B45" s="21"/>
       <c r="C45" s="22"/>
@@ -16216,7 +16216,7 @@
       </c>
       <c r="U45" s="22"/>
     </row>
-    <row r="46" ht="56" customHeight="1">
+    <row r="46" ht="152.99" customHeight="true">
       <c r="A46" s="0"/>
       <c r="B46" s="21"/>
       <c r="C46" s="22"/>
@@ -16253,7 +16253,7 @@
       </c>
       <c r="U46" s="22"/>
     </row>
-    <row r="47" ht="56" customHeight="1">
+    <row r="47" ht="152.99" customHeight="true">
       <c r="A47" s="0"/>
       <c r="B47" s="21"/>
       <c r="C47" s="22"/>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="U47" s="22"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="152.99" customHeight="true">
       <c r="A48" s="0"/>
       <c r="B48" s="21"/>
       <c r="C48" s="22"/>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="U48" s="22"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="152.99" customHeight="true">
       <c r="A49" s="0"/>
       <c r="B49" s="21"/>
       <c r="C49" s="22"/>
@@ -16374,7 +16374,7 @@
       </c>
       <c r="U49" s="22"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="152.99" customHeight="true">
       <c r="A50" s="0"/>
       <c r="B50" s="21"/>
       <c r="C50" s="22"/>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="U50" s="22"/>
     </row>
-    <row r="51" ht="56" customHeight="1">
+    <row r="51" ht="152.99" customHeight="true">
       <c r="A51" s="0"/>
       <c r="B51" s="21"/>
       <c r="C51" s="22"/>
@@ -16458,7 +16458,7 @@
       </c>
       <c r="U51" s="22"/>
     </row>
-    <row r="52" ht="56" customHeight="1">
+    <row r="52" ht="152.99" customHeight="true">
       <c r="A52" s="0"/>
       <c r="B52" s="21"/>
       <c r="C52" s="22"/>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="U52" s="22"/>
     </row>
-    <row r="53" ht="56" customHeight="1">
+    <row r="53" ht="152.99" customHeight="true">
       <c r="A53" s="0"/>
       <c r="B53" s="21"/>
       <c r="C53" s="22"/>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="U53" s="22"/>
     </row>
-    <row r="54" ht="56" customHeight="1">
+    <row r="54" ht="152.99" customHeight="true">
       <c r="A54" s="0"/>
       <c r="B54" s="21"/>
       <c r="C54" s="22"/>
@@ -16577,7 +16577,7 @@
       </c>
       <c r="U54" s="22"/>
     </row>
-    <row r="55" ht="56" customHeight="1">
+    <row r="55" ht="152.99" customHeight="true">
       <c r="A55" s="0"/>
       <c r="B55" s="21"/>
       <c r="C55" s="22"/>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="U55" s="22"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="152.99" customHeight="true">
       <c r="A56" s="0"/>
       <c r="B56" s="21"/>
       <c r="C56" s="22"/>
@@ -16673,7 +16673,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="14" max="16383" man="1"/>
     <brk id="28" max="16383" man="1"/>
